--- a/import/Import Teilnehmer BOP.xlsx
+++ b/import/Import Teilnehmer BOP.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\zbb\import\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp2\htdocs\matrix\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>2026</v>
@@ -687,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>2026</v>
@@ -719,7 +719,7 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>2026</v>
@@ -751,7 +751,7 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>2026</v>
@@ -783,7 +783,7 @@
         <v>1</v>
       </c>
       <c r="G11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>2026</v>
@@ -815,7 +815,7 @@
         <v>1</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>2026</v>
@@ -847,7 +847,7 @@
         <v>1</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <v>2026</v>
@@ -879,7 +879,7 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <v>2026</v>
@@ -911,7 +911,7 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H15">
         <v>2026</v>
@@ -943,7 +943,7 @@
         <v>1</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <v>2026</v>
@@ -975,7 +975,7 @@
         <v>1</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17">
         <v>2026</v>
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18">
         <v>2026</v>
@@ -1039,7 +1039,7 @@
         <v>1</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19">
         <v>2026</v>
@@ -1071,7 +1071,7 @@
         <v>1</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20">
         <v>2026</v>
@@ -1103,7 +1103,7 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21">
         <v>2026</v>
@@ -1135,7 +1135,7 @@
         <v>1</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22">
         <v>2026</v>
@@ -1167,7 +1167,7 @@
         <v>1</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H23">
         <v>2026</v>
@@ -1199,7 +1199,7 @@
         <v>1</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H24">
         <v>2026</v>
@@ -1231,7 +1231,7 @@
         <v>1</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H25">
         <v>2026</v>
@@ -1263,7 +1263,7 @@
         <v>1</v>
       </c>
       <c r="G26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H26">
         <v>2026</v>
